--- a/output/graficos_dimensiones/comunal_migracion_flujos_od_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_migracion_flujos_od_2024_biobio.xlsx
@@ -918,7 +918,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:32</t>
+    <t xml:space="preserve">2026-09-18 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_migracion_flujos_od_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_migracion_flujos_od_2024_biobio.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">273</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">158</t>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">58</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">1008</t>
@@ -918,7 +918,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:12</t>
+    <t xml:space="preserve">2026-10-05 04:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
